--- a/Test Results/Excel/Execution_Summary.xlsx
+++ b/Test Results/Excel/Execution_Summary.xlsx
@@ -480,7 +480,7 @@
         <v>Execution Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.33s</v>
+        <v>0.31s</v>
       </c>
     </row>
     <row r="11">

--- a/Test Results/Excel/Execution_Summary.xlsx
+++ b/Test Results/Excel/Execution_Summary.xlsx
@@ -440,7 +440,7 @@
         <v>Passed</v>
       </c>
       <c r="B5">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6">
@@ -448,7 +448,7 @@
         <v>Failed</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -456,7 +456,7 @@
         <v>Skipped</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -472,7 +472,7 @@
         <v>Pass Rate (%)</v>
       </c>
       <c r="B9" t="str">
-        <v>99.22%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="10">
@@ -480,7 +480,7 @@
         <v>Execution Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.31s</v>
+        <v>0.33s</v>
       </c>
     </row>
     <row r="11">
